--- a/PartsListUS_251003.xlsx
+++ b/PartsListUS_251003.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Box\AnisLab\Homepage\operanthouse\HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78BB6F4-BBE1-4426-BB28-F219C9713913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E18AEB9-F0EF-4B04-87A2-2ED1CE780801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="5330" windowWidth="21580" windowHeight="25670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2450" yWindow="10950" windowWidth="17720" windowHeight="24540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MainParts" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="273">
   <si>
     <t>Name</t>
     <phoneticPr fontId="2"/>
@@ -895,18 +895,6 @@
   </si>
   <si>
     <t>Single board linux computer</t>
-  </si>
-  <si>
-    <t>Wheel weights</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/CK-Auto-Adhesive-EasyPeel-Tape-Low/dp/B072JXSN9P/ref=sr_1_4?crid=WRRN64YZH5N3&amp;dib=eyJ2IjoiMSJ9.gYsY9rU1ci-xYPj1jLXm-yDhxhuMCoi5Ejf2RcxuO0a2bn0xE2eW1Y601VBUf6vXcrQev9YMK9QMb-4rFsgXqIKfZnDiLZG82M5p3QExAQC12j-Bv1clax45zaweAXWOANh4NW-AcYjeN30YtyZ5uLoSseAupAx2qgBUPsbtDGCZW7BMNhHTRtTrTerks7vjoYkTJ5vRDBja7QuKuOdVp2kqArk6NkvG16a-V3nc1pw.rEow4my0-WA6uH6VL8a7Xef1fam-938zdEXooDGjwXI&amp;dib_tag=se&amp;keywords=wheel%2Bweight&amp;qid=1764201760&amp;sprefix=wheele%2Bweight%2Caps%2C97&amp;sr=8-4&amp;th=1</t>
-  </si>
-  <si>
-    <t>CKAuto 1oz, Grey, Adhesive Stick on Wheel Weights,EasyPeel Tape, 72 oz/Box, US Quality(72pcs)</t>
-  </si>
-  <si>
-    <t>Adhensive stick on wheel weights</t>
   </si>
 </sst>
 </file>
@@ -1440,8 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:M105"/>
+  <dimension ref="A2:M103"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="23.83203125" style="2" customWidth="1"/>
@@ -1472,7 +1459,7 @@
       </c>
       <c r="K4" s="3">
         <f>SUM(K6:K108)</f>
-        <v>364.46222152777784</v>
+        <v>359.72444375000009</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>228</v>
@@ -2987,87 +2974,90 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="2:13">
-      <c r="C82" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F82" s="1" t="s">
+    <row r="83" spans="2:13">
+      <c r="C83" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H82" s="1">
-        <v>72</v>
-      </c>
-      <c r="I82" s="1">
-        <v>16</v>
-      </c>
-      <c r="J82" s="3">
-        <v>21.32</v>
-      </c>
-      <c r="K82" s="1">
-        <f>J82*I82/H82</f>
-        <v>4.7377777777777776</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>274</v>
-      </c>
+      <c r="G83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1</v>
+      </c>
+      <c r="J83" s="17">
+        <v>13.99</v>
+      </c>
+      <c r="K83" s="1">
+        <f>J83*I83/H83</f>
+        <v>13.99</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="M83" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13">
+      <c r="J84" s="17"/>
     </row>
     <row r="85" spans="2:13">
       <c r="B85" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H85" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I85" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J85" s="17">
-        <v>13.99</v>
+        <v>8.75</v>
       </c>
       <c r="K85" s="1">
         <f>J85*I85/H85</f>
-        <v>13.99</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>150</v>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13">
-      <c r="J86" s="17"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="87" spans="2:13">
       <c r="C87" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -3076,17 +3066,17 @@
         <v>100</v>
       </c>
       <c r="I87" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J87" s="17">
-        <v>8.75</v>
+        <v>6.56</v>
       </c>
       <c r="K87" s="1">
         <f>J87*I87/H87</f>
-        <v>0.52500000000000002</v>
+        <v>0.52479999999999993</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>178</v>
@@ -3094,82 +3084,82 @@
     </row>
     <row r="89" spans="2:13">
       <c r="C89" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="G89" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H89" s="1">
         <v>100</v>
       </c>
       <c r="I89" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J89" s="17">
-        <v>6.56</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K89" s="1">
         <f>J89*I89/H89</f>
-        <v>0.52479999999999993</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="2:13">
       <c r="C91" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="H91" s="1">
         <v>100</v>
       </c>
       <c r="I91" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J91" s="17">
-        <v>4.4000000000000004</v>
+        <v>2.06</v>
       </c>
       <c r="K91" s="1">
         <f>J91*I91/H91</f>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>54</v>
+        <v>0.12359999999999999</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="2:13">
       <c r="C93" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>23</v>
@@ -3178,107 +3168,107 @@
         <v>100</v>
       </c>
       <c r="I93" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J93" s="17">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="K93" s="1">
         <f>J93*I93/H93</f>
-        <v>0.12359999999999999</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>63</v>
+        <v>0.12869999999999998</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="M93" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="95" spans="2:13">
-      <c r="C95" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="1">
-        <v>100</v>
-      </c>
-      <c r="I95" s="1">
-        <v>11</v>
-      </c>
-      <c r="J95" s="17">
-        <v>1.17</v>
-      </c>
-      <c r="K95" s="1">
-        <f>J95*I95/H95</f>
-        <v>0.12869999999999998</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M95" s="5" t="s">
-        <v>179</v>
-      </c>
+    <row r="94" spans="2:13">
+      <c r="J94" s="17"/>
     </row>
     <row r="96" spans="2:13">
-      <c r="J96" s="17"/>
+      <c r="C96" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H96" s="1">
+        <v>16</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1</v>
+      </c>
+      <c r="J96" s="17">
+        <v>57.99</v>
+      </c>
+      <c r="K96" s="1">
+        <f>J96*I96/H96</f>
+        <v>3.6243750000000001</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="M96" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="C97" s="1"/>
     </row>
     <row r="98" spans="1:13">
       <c r="C98" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H98" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I98" s="1">
         <v>1</v>
       </c>
-      <c r="J98" s="17">
-        <v>57.99</v>
+      <c r="J98" s="20">
+        <v>8.49</v>
       </c>
       <c r="K98" s="1">
         <f>J98*I98/H98</f>
-        <v>3.6243750000000001</v>
+        <v>8.49</v>
       </c>
       <c r="L98" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:13">
-      <c r="C99" s="1"/>
+      <c r="J99" s="17"/>
     </row>
     <row r="100" spans="1:13">
       <c r="C100" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H100" s="1">
         <v>1</v>
       </c>
@@ -3286,112 +3276,79 @@
         <v>1</v>
       </c>
       <c r="J100" s="20">
-        <v>8.49</v>
+        <v>7.99</v>
       </c>
       <c r="K100" s="1">
         <f>J100*I100/H100</f>
-        <v>8.49</v>
-      </c>
-      <c r="L100" s="9" t="s">
-        <v>151</v>
+        <v>7.99</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="J101" s="17"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="6" customFormat="1">
+      <c r="A101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="J101" s="22"/>
+      <c r="M101" s="5"/>
     </row>
     <row r="102" spans="1:13">
       <c r="C102" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F102" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H102" s="1">
-        <v>1</v>
-      </c>
-      <c r="I102" s="1">
-        <v>1</v>
-      </c>
-      <c r="J102" s="20">
-        <v>7.99</v>
-      </c>
-      <c r="K102" s="1">
+      <c r="G102" s="6"/>
+      <c r="H102" s="6">
+        <v>1</v>
+      </c>
+      <c r="I102" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J102" s="22">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="K102" s="6">
         <f>J102*I102/H102</f>
-        <v>7.99</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>56</v>
+        <v>9.4949999999999992</v>
+      </c>
+      <c r="L102" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" s="6" customFormat="1">
-      <c r="A103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="J103" s="22"/>
-      <c r="M103" s="5"/>
-    </row>
-    <row r="104" spans="1:13">
-      <c r="C104" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F104" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="D103" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6">
-        <v>1</v>
-      </c>
-      <c r="I104" s="6">
+      <c r="H103" s="1">
+        <v>1</v>
+      </c>
+      <c r="I103" s="1">
         <v>0.5</v>
       </c>
-      <c r="J104" s="22">
-        <v>18.989999999999998</v>
-      </c>
-      <c r="K104" s="6">
-        <f>J104*I104/H104</f>
-        <v>9.4949999999999992</v>
-      </c>
-      <c r="L104" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="M104" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="D105" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="1">
-        <v>1</v>
-      </c>
-      <c r="I105" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J105" s="3">
+      <c r="J103" s="3">
         <v>16.989999999999998</v>
       </c>
-      <c r="L105" s="1" t="s">
+      <c r="L103" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M105" s="5" t="s">
+      <c r="M103" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3404,12 +3361,12 @@
     <hyperlink ref="L55" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="L35" r:id="rId5" display="https://www.amazon.com/dp/B07ZV8FWM4/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B07ZV8FWM4&amp;pd_rd_w=ymGCh&amp;pf_rd_p=48d372c1-f7e1-4b8b-9d02-4bd86f5158c5&amp;pd_rd_wg=RlFbL&amp;pf_rd_r=VZN6AZT5117MXZTD12Z1&amp;pd_rd_r=3c7db60a-5271-41cd-89fc-05c6ac8cd662&amp;spLa=ZW5jcnlwdGVkUXVhbGlmaWVyPUExMlhQNDgyM0dTU1ImZW5jcnlwdGVkSWQ9QTA4Mzg4NzkzSjRTQlE1ODJIQllQJmVuY3J5cHRlZEFkSWQ9QTA5MTY1MjYxRTRBWjZZOVU5TEtOJndpZGdldE5hbWU9c3BfZGV0YWlsJmFjdGlvbj1jbGlja1JlZGlyZWN0JmRvTm90TG9nQ2xpY2s9dHJ1ZQ==" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="L6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="L93" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="L91" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="L26" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="L32" r:id="rId9" xr:uid="{221BCB36-3FA1-4B49-834A-981F436227B5}"/>
     <hyperlink ref="L33" r:id="rId10" xr:uid="{83A441C0-DDC5-462C-BD8E-08A491379DB8}"/>
     <hyperlink ref="L69" r:id="rId11" display="https://www.amazon.com/Wishiot-Digital-Waterproof-Robotic-Crawler/dp/B08DCHGRXG/ref=sr_1_2_sspa?dchild=1&amp;keywords=DS3225MG&amp;qid=1625162309&amp;s=toys-and-games&amp;sr=1-2-spons&amp;psc=1&amp;spLa=ZW5jcnlwdGVkUXVhbGlmaWVyPUFXRE9ITzVLOTRJNkEmZW5jcnlwdGVkSWQ9QTA4MjE1OTAySjBCNENOVlY2VkFaJmVuY3J5cHRlZEFkSWQ9QTAwMzUyODMzUkdGT0VPSkdEV1c2JndpZGdldE5hbWU9c3BfYXRmJmFjdGlvbj1jbGlja1JlZGlyZWN0JmRvTm90TG9nQ2xpY2s9dHJ1ZQ==" xr:uid="{08D431BD-5DCB-4C13-8C96-2504AA01045C}"/>
-    <hyperlink ref="L104" r:id="rId12" xr:uid="{D233AFE0-2981-442B-B27A-CDB229A85F4F}"/>
+    <hyperlink ref="L102" r:id="rId12" xr:uid="{D233AFE0-2981-442B-B27A-CDB229A85F4F}"/>
     <hyperlink ref="L18" r:id="rId13" xr:uid="{215060F0-0765-44AA-86FE-E68039DD4A00}"/>
     <hyperlink ref="L42" r:id="rId14" xr:uid="{F4CBD0C9-C04F-4C72-AE9F-CA71ABCE6F3D}"/>
     <hyperlink ref="L63" r:id="rId15" display="https://www.amazon.com/Elegoo-EL-CP-004-Multicolored-Breadboard-arduino/dp/B01EV70C78/ref=sr_1_1_sspa?dchild=1&amp;keywords=elegoo+el-cp-004+120+pcs+m&amp;qid=1591230109&amp;s=electronics&amp;sr=1-1-spons&amp;psc=1&amp;spLa=ZW5jcnlwdGVkUXVhbGlmaWVyPUExRTZFVTk4TU9PT1IxJmVuY3J5cHRlZElkPUEwMTU5MTEzMzcyTjBHOUs1Q1BTTiZlbmNyeXB0ZWRBZElkPUEwNDI3MjEzMTJHUEU4R1E1UldSNCZ3aWRnZXROYW1lPXNwX2F0ZiZhY3Rpb249Y2xpY2tSZWRpcmVjdCZkb05vdExvZ0NsaWNrPXRydWU=" xr:uid="{703B8DB7-AD61-47FE-BC00-68ED6644026B}"/>
@@ -3417,10 +3374,10 @@
     <hyperlink ref="L45" r:id="rId17" xr:uid="{05EE3074-BEA3-4865-B6FF-00E08D736877}"/>
     <hyperlink ref="L39" r:id="rId18" display="https://www.amazon.com/BOJACK-Values-Resistor-Resistors-Assortment/dp/B08FD1XVL6/ref=sr_1_3?crid=H0MAGTHHPRJP&amp;dib=eyJ2IjoiMSJ9.9auwJDD1kOZT_VAxZUQqv68sa9cmYqIz_iW09viGKDXYun-w1X0UVfnwMTATpW1Avsb5Yf_v6bLpK9xv4jsMNzKtKcyvSthOJH1_dfjBBfVYt-ecrv8B3zaL0-ywDXBE9fHgGDjC1JIGM8Ikvly274FvucUniXIrgdK5xH4mPR9PvD5OeCQpqA-UG7nCRoHW--KiqexIHkYAXU35d_kXKXLO4ziU69WcEkjAbBXqkdI.hP8wJKmPn_L_bvGCDCUoAXsHvDHf2dLjNJlCGI7-Yu0&amp;dib_tag=se&amp;keywords=Carbon%2BFilm%2BResistors&amp;qid=1747170259&amp;sprefix=carbon%2Bfilm%2Bresistors%2Caps%2C130&amp;sr=8-3&amp;th=1" xr:uid="{7415DE56-6D48-4051-98C6-F22253AE06C2}"/>
     <hyperlink ref="L38" r:id="rId19" xr:uid="{72B5393E-E55A-4118-B558-FE9FD38D3FB5}"/>
-    <hyperlink ref="L98" r:id="rId20" xr:uid="{E4FC3CED-23AC-4189-B097-1549806D8006}"/>
+    <hyperlink ref="L96" r:id="rId20" xr:uid="{E4FC3CED-23AC-4189-B097-1549806D8006}"/>
     <hyperlink ref="L72" r:id="rId21" xr:uid="{BBBFA104-FE5C-4B60-963A-54E5568224B0}"/>
-    <hyperlink ref="L85" r:id="rId22" xr:uid="{EC617107-D620-407E-9DAC-38CC51F50C7B}"/>
-    <hyperlink ref="L100" r:id="rId23" xr:uid="{32FDFF6B-E310-4EED-B85D-25CF176DF01F}"/>
+    <hyperlink ref="L83" r:id="rId22" xr:uid="{EC617107-D620-407E-9DAC-38CC51F50C7B}"/>
+    <hyperlink ref="L98" r:id="rId23" xr:uid="{32FDFF6B-E310-4EED-B85D-25CF176DF01F}"/>
     <hyperlink ref="L76" r:id="rId24" xr:uid="{A96B24A2-34BA-4B79-A124-6BEFB0128EA8}"/>
     <hyperlink ref="L78" r:id="rId25" xr:uid="{0934168A-7A5E-438E-BF02-882B2525CB0A}"/>
     <hyperlink ref="L50" r:id="rId26" xr:uid="{5DB9F699-13C8-4C60-BDF4-F0CFBA4D9813}"/>
@@ -3437,7 +3394,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5F0927-622F-4F79-8B1D-D017C685B316}">
-  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L82"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.5"/>
   <cols>
